--- a/artfynd/A 24335-2022 artfynd.xlsx
+++ b/artfynd/A 24335-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156771</v>
       </c>
       <c r="B2" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24335-2022 artfynd.xlsx
+++ b/artfynd/A 24335-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156771</v>
       </c>
       <c r="B2" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156772</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156773</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156775</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156776</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136156781</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136156779</v>
       </c>
       <c r="B8" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136156780</v>
       </c>
       <c r="B10" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 24335-2022 artfynd.xlsx
+++ b/artfynd/A 24335-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156771</v>
       </c>
       <c r="B2" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156772</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156773</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156775</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156776</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136156781</v>
       </c>
       <c r="B7" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136156779</v>
       </c>
       <c r="B8" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136156780</v>
       </c>
       <c r="B10" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 24335-2022 artfynd.xlsx
+++ b/artfynd/A 24335-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156771</v>
       </c>
       <c r="B2" t="n">
-        <v>89439</v>
+        <v>89440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156772</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156773</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156775</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156776</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136156781</v>
       </c>
       <c r="B7" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136156779</v>
       </c>
       <c r="B8" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>136156780</v>
       </c>
       <c r="B10" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
